--- a/data-raw/jayaraman.bamboo.xlsx
+++ b/data-raw/jayaraman.bamboo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\drop\rpack\agridat\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921555CF-B38D-48AA-A97C-55745FA626B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CAEE764-E67D-48E4-A315-D75B56F10500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2860" yWindow="1820" windowWidth="7590" windowHeight="8130" xr2:uid="{6FF44BF4-A841-480A-9F33-0161B06E98EF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{6FF44BF4-A841-480A-9F33-0161B06E98EF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="20">
   <si>
     <t>block</t>
   </si>
@@ -70,6 +70,27 @@
   </si>
   <si>
     <t>loc</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>F5</t>
+  </si>
+  <si>
+    <t>F6</t>
   </si>
 </sst>
 </file>
@@ -437,6 +458,24 @@
       <c r="C1" t="s">
         <v>10</v>
       </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
@@ -562,7 +601,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>95</v>
@@ -736,7 +775,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D12">
         <v>60</v>
@@ -910,7 +949,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D18">
         <v>152</v>
@@ -1084,7 +1123,7 @@
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D24">
         <v>20</v>
@@ -1258,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D30">
         <v>99</v>
@@ -1432,7 +1471,7 @@
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D36">
         <v>100</v>
